--- a/frontend/dist/formats/osc_format.xlsx
+++ b/frontend/dist/formats/osc_format.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\visha\Downloads\SG ENCON\OSC Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E180F0C-9C84-401B-AB3F-0F1C10D6A090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C782CF3C-6971-4816-A649-19358097C00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{32E78001-1896-471F-9DD0-2ACB2EBEDC5A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="52">
   <si>
     <t>REGION</t>
   </si>
@@ -54,9 +54,6 @@
     <t>JC_SAP_ID</t>
   </si>
   <si>
-    <t>CMP_NAME</t>
-  </si>
-  <si>
     <t>LSM_NAME</t>
   </si>
   <si>
@@ -88,6 +85,111 @@
   </si>
   <si>
     <t>Equipment Vendor</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Delhi-1 (West)</t>
+  </si>
+  <si>
+    <t>Delhi-2 (South)</t>
+  </si>
+  <si>
+    <t>Delhi-3 (Central-East)</t>
+  </si>
+  <si>
+    <t>Delhi-4 (North)</t>
+  </si>
+  <si>
+    <t>Faridabad (NCR)</t>
+  </si>
+  <si>
+    <t>Ghaziabad (NCR)</t>
+  </si>
+  <si>
+    <t>Gurgaon (NCR)</t>
+  </si>
+  <si>
+    <t>Noida (NCR)</t>
+  </si>
+  <si>
+    <t>Punjab</t>
+  </si>
+  <si>
+    <t>Amritsar</t>
+  </si>
+  <si>
+    <t>Bathinda</t>
+  </si>
+  <si>
+    <t>Chandigarh</t>
+  </si>
+  <si>
+    <t>Jalandhar</t>
+  </si>
+  <si>
+    <t>Ludhiana-1</t>
+  </si>
+  <si>
+    <t>Ludhiana-2</t>
+  </si>
+  <si>
+    <t>Pathankot</t>
+  </si>
+  <si>
+    <t>Patiala</t>
+  </si>
+  <si>
+    <t>Sangrur</t>
+  </si>
+  <si>
+    <t>Haryana</t>
+  </si>
+  <si>
+    <t>Ambala</t>
+  </si>
+  <si>
+    <t>Hissar</t>
+  </si>
+  <si>
+    <t>Karnal</t>
+  </si>
+  <si>
+    <t>Panipat</t>
+  </si>
+  <si>
+    <t>Palwal</t>
+  </si>
+  <si>
+    <t>Rewari</t>
+  </si>
+  <si>
+    <t>Rohtak</t>
+  </si>
+  <si>
+    <t>UP East</t>
+  </si>
+  <si>
+    <t>Allahabad</t>
+  </si>
+  <si>
+    <t>Azamgarh</t>
+  </si>
+  <si>
+    <t>Faizabad</t>
+  </si>
+  <si>
+    <t>Gorakhpur</t>
+  </si>
+  <si>
+    <t>Raibareilly</t>
+  </si>
+  <si>
+    <t>Varanasi</t>
   </si>
 </sst>
 </file>
@@ -168,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -182,6 +284,10 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,63 +602,303 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA57586D-1ADE-485B-861E-6E9C06AA98C1}">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
-        <v>17</v>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
